--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126533661</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126533705</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126533698</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>126533690</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126533702</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>126533700</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>126533660</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>126533688</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126533717</v>
       </c>
       <c r="B10" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>126533728</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>126533727</v>
       </c>
       <c r="B12" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>126533699</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126533677</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>126533675</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126533716</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>126533718</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>126533678</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126533697</v>
       </c>
       <c r="B19" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>126533663</v>
       </c>
       <c r="B20" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>126533707</v>
       </c>
       <c r="B21" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>126533691</v>
       </c>
       <c r="B23" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>126533659</v>
       </c>
       <c r="B24" t="n">
-        <v>56849</v>
+        <v>57044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -2863,7 +2863,7 @@
         <v>126533706</v>
       </c>
       <c r="B22" t="n">
-        <v>57076</v>
+        <v>57078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -2863,7 +2863,7 @@
         <v>126533706</v>
       </c>
       <c r="B22" t="n">
-        <v>57078</v>
+        <v>57079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -2863,7 +2863,7 @@
         <v>126533706</v>
       </c>
       <c r="B22" t="n">
-        <v>57079</v>
+        <v>57082</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -2863,7 +2863,7 @@
         <v>126533706</v>
       </c>
       <c r="B22" t="n">
-        <v>57082</v>
+        <v>57083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126533661</v>
+        <v>126533659</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523099</v>
+        <v>523024</v>
       </c>
       <c r="R2" t="n">
-        <v>6614490</v>
+        <v>6614464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126533705</v>
+        <v>126533697</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,14 +814,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523007</v>
+        <v>523031</v>
       </c>
       <c r="R3" t="n">
-        <v>6614624</v>
+        <v>6614414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
         <v>126533698</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126533690</v>
+        <v>126533699</v>
       </c>
       <c r="B5" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523106</v>
+        <v>523008</v>
       </c>
       <c r="R5" t="n">
-        <v>6614600</v>
+        <v>6614605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1085,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ändtarmstömning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126533702</v>
+        <v>126533705</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1158,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523221</v>
+        <v>523007</v>
       </c>
       <c r="R6" t="n">
-        <v>6614411</v>
+        <v>6614624</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126533700</v>
+        <v>126533706</v>
       </c>
       <c r="B7" t="n">
-        <v>57073</v>
+        <v>57144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,26 +1236,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1267,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523098</v>
+        <v>523034</v>
       </c>
       <c r="R7" t="n">
-        <v>6614638</v>
+        <v>6614584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1337,7 @@
         <v>126533660</v>
       </c>
       <c r="B8" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126533688</v>
+        <v>126533661</v>
       </c>
       <c r="B9" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1473,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1485,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523105</v>
+        <v>523099</v>
       </c>
       <c r="R9" t="n">
-        <v>6614453</v>
+        <v>6614490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126533717</v>
+        <v>126533663</v>
       </c>
       <c r="B10" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1582,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523135</v>
+        <v>523193</v>
       </c>
       <c r="R10" t="n">
-        <v>6614654</v>
+        <v>6614433</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126533728</v>
+        <v>126533667</v>
       </c>
       <c r="B11" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,14 +1691,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1703,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523103</v>
+        <v>523247</v>
       </c>
       <c r="R11" t="n">
-        <v>6614544</v>
+        <v>6614470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126533727</v>
+        <v>126533675</v>
       </c>
       <c r="B12" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1800,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1812,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523120</v>
+        <v>523101</v>
       </c>
       <c r="R12" t="n">
-        <v>6614598</v>
+        <v>6614468</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,10 +1879,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126533699</v>
+        <v>126533677</v>
       </c>
       <c r="B13" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1909,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1921,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523008</v>
+        <v>523132</v>
       </c>
       <c r="R13" t="n">
-        <v>6614605</v>
+        <v>6614657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,11 +1962,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ändtarmstömning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126533677</v>
+        <v>126533678</v>
       </c>
       <c r="B14" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523132</v>
+        <v>523208</v>
       </c>
       <c r="R14" t="n">
-        <v>6614657</v>
+        <v>6614463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126533675</v>
+        <v>126533688</v>
       </c>
       <c r="B15" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523101</v>
+        <v>523105</v>
       </c>
       <c r="R15" t="n">
-        <v>6614468</v>
+        <v>6614453</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126533716</v>
+        <v>126533690</v>
       </c>
       <c r="B16" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,14 +2236,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523120</v>
+        <v>523106</v>
       </c>
       <c r="R16" t="n">
-        <v>6614607</v>
+        <v>6614600</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126533718</v>
+        <v>126533691</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523213</v>
+        <v>523190</v>
       </c>
       <c r="R17" t="n">
-        <v>6614482</v>
+        <v>6614423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126533678</v>
+        <v>126533700</v>
       </c>
       <c r="B18" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523208</v>
+        <v>523098</v>
       </c>
       <c r="R18" t="n">
-        <v>6614463</v>
+        <v>6614638</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126533697</v>
+        <v>126533702</v>
       </c>
       <c r="B19" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,14 +2563,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523031</v>
+        <v>523221</v>
       </c>
       <c r="R19" t="n">
-        <v>6614414</v>
+        <v>6614411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126533663</v>
+        <v>126533707</v>
       </c>
       <c r="B20" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523193</v>
+        <v>523223</v>
       </c>
       <c r="R20" t="n">
-        <v>6614433</v>
+        <v>6614522</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2751,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126533707</v>
+        <v>126533716</v>
       </c>
       <c r="B21" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523223</v>
+        <v>523120</v>
       </c>
       <c r="R21" t="n">
-        <v>6614522</v>
+        <v>6614607</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126533706</v>
+        <v>126533717</v>
       </c>
       <c r="B22" t="n">
-        <v>57083</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,26 +2871,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523034</v>
+        <v>523135</v>
       </c>
       <c r="R22" t="n">
-        <v>6614584</v>
+        <v>6614654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126533691</v>
+        <v>126533718</v>
       </c>
       <c r="B23" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523190</v>
+        <v>523213</v>
       </c>
       <c r="R23" t="n">
-        <v>6614423</v>
+        <v>6614482</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126533659</v>
+        <v>126533727</v>
       </c>
       <c r="B24" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523024</v>
+        <v>523120</v>
       </c>
       <c r="R24" t="n">
-        <v>6614464</v>
+        <v>6614598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3184,6 +3184,115 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126533728</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Morskoga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>523103</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6614544</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Robert Petersen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42629-2025 artfynd.xlsx
+++ b/artfynd/A 42629-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533659</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533660</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533661</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533663</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533675</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533677</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533678</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533688</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533690</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533691</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1980,6 +2040,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533697</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533698</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533699</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533700</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533702</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533705</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2639,6 +2729,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533707</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2748,6 +2843,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533716</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,6 +2957,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533717</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2966,6 +3071,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533718</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3075,6 +3185,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533727</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3184,6 +3299,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533728</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3293,8 +3413,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126533706</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>